--- a/data/demo/Север бригады.xlsx
+++ b/data/demo/Север бригады.xlsx
@@ -464,7 +464,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Усиевича, д. 1А</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -482,7 +486,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Город Москва, проезд.Старый Зыковский, д. 6 к 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,7 +508,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Черняховского, д. 9 к 3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,7 +530,11 @@
           <t>Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Верхняя Масловка, д. 4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,7 +552,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Город Москва, ш.Волоколамское, д. 8</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -554,7 +574,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Новопесчаная, д. 23 к 3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -572,7 +596,11 @@
           <t>Ремонт, Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Нарвская, д. 11 к 2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -590,7 +618,11 @@
           <t>Ремонт, Аварии</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Город Москва, пер.Большой Кондратьевский, д. 8с1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,7 +640,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Нижняя, д. 11</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -626,7 +662,11 @@
           <t>Ремонт, Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Город Москва, проезд.3-й Хорошёвский, д. 8</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -644,7 +684,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Вятская, д. 3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -662,7 +706,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Зорге, д. 16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
